--- a/tams-cfets/src/main/resources/tpl/DAYREGEXPORTTPL.xlsx
+++ b/tams-cfets/src/main/resources/tpl/DAYREGEXPORTTPL.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23628"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\tams-3.0\tams-cfets\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FF930B-B509-423E-82C3-910C24979188}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="本币交易" sheetId="1" r:id="rId1"/>
@@ -113,9 +119,6 @@
     <t>{.settleSpeedStr}</t>
   </si>
   <si>
-    <t>{.intAmt}</t>
-  </si>
-  <si>
     <t>{.interest}</t>
   </si>
   <si>
@@ -127,20 +130,20 @@
   <si>
     <t>{.settleTypeStr}</t>
   </si>
+  <si>
+    <t>{.unitInt}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.0000"/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,150 +170,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -321,8 +180,22 @@
       <name val="等线"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -331,192 +204,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -539,263 +232,21 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -817,7 +268,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="43" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -830,64 +281,23 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="3">
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="Normal 3 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="Normal 3 2" xfId="35"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="36" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="37" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="38" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="39" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="40" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="41" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="42" builtinId="42"/>
-    <cellStyle name="Normal 2" xfId="43"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="44" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="45" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="46" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="47" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="48" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="49" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="50" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1145,35 +555,35 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P345"/>
-  <sheetFormatPr defaultColWidth="9.10833333333333" defaultRowHeight="17.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.25" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1083333333333" style="2" customWidth="1"/>
-    <col min="3" max="3" width="24.775" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.1083333333333" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.8833333333333" style="2" customWidth="1"/>
+    <col min="1" max="1" width="21.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="24.77734375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" style="2" customWidth="1"/>
     <col min="6" max="6" width="27" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.6666666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" style="2" customWidth="1"/>
     <col min="8" max="8" width="15" style="2" customWidth="1"/>
-    <col min="9" max="9" width="19.6666666666667" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.8833333333333" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.775" style="2" customWidth="1"/>
-    <col min="12" max="12" width="19.2166666666667" style="2" customWidth="1"/>
-    <col min="13" max="13" width="18.3333333333333" style="2" customWidth="1"/>
-    <col min="14" max="14" width="25.775" style="2" customWidth="1"/>
-    <col min="15" max="15" width="22.775" style="2" customWidth="1"/>
-    <col min="16" max="16" width="16.1083333333333" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="9.10833333333333" style="2"/>
+    <col min="9" max="9" width="19.6640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.77734375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="19.21875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="25.77734375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="22.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="16.109375" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="35.25" customHeight="1" spans="1:16">
+    <row r="1" spans="1:16" s="1" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1223,7 +633,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:16">
+    <row r="2" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>16</v>
       </c>
@@ -1257,23 +667,23 @@
       <c r="K2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -1291,7 +701,7 @@
       <c r="O3" s="6"/>
       <c r="P3" s="10"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1309,7 +719,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="10"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -1327,7 +737,7 @@
       <c r="O5" s="6"/>
       <c r="P5" s="10"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -1345,7 +755,7 @@
       <c r="O6" s="6"/>
       <c r="P6" s="10"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1363,7 +773,7 @@
       <c r="O7" s="6"/>
       <c r="P7" s="10"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -1381,7 +791,7 @@
       <c r="O8" s="6"/>
       <c r="P8" s="10"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1399,7 +809,7 @@
       <c r="O9" s="6"/>
       <c r="P9" s="10"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -1417,7 +827,7 @@
       <c r="O10" s="6"/>
       <c r="P10" s="10"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1435,7 +845,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="10"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1453,7 +863,7 @@
       <c r="O12" s="6"/>
       <c r="P12" s="10"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1471,7 +881,7 @@
       <c r="O13" s="6"/>
       <c r="P13" s="10"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1489,7 +899,7 @@
       <c r="O14" s="6"/>
       <c r="P14" s="10"/>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1507,7 +917,7 @@
       <c r="O15" s="6"/>
       <c r="P15" s="10"/>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1525,7 +935,7 @@
       <c r="O16" s="6"/>
       <c r="P16" s="10"/>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -1543,7 +953,7 @@
       <c r="O17" s="6"/>
       <c r="P17" s="10"/>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -1561,7 +971,7 @@
       <c r="O18" s="6"/>
       <c r="P18" s="10"/>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -1579,7 +989,7 @@
       <c r="O19" s="6"/>
       <c r="P19" s="10"/>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -1597,7 +1007,7 @@
       <c r="O20" s="6"/>
       <c r="P20" s="10"/>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1615,7 +1025,7 @@
       <c r="O21" s="6"/>
       <c r="P21" s="10"/>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -1633,7 +1043,7 @@
       <c r="O22" s="6"/>
       <c r="P22" s="10"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -1651,7 +1061,7 @@
       <c r="O23" s="6"/>
       <c r="P23" s="10"/>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -1669,7 +1079,7 @@
       <c r="O24" s="6"/>
       <c r="P24" s="10"/>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -1687,7 +1097,7 @@
       <c r="O25" s="6"/>
       <c r="P25" s="10"/>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -1705,7 +1115,7 @@
       <c r="O26" s="6"/>
       <c r="P26" s="10"/>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -1723,7 +1133,7 @@
       <c r="O27" s="6"/>
       <c r="P27" s="10"/>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -1741,7 +1151,7 @@
       <c r="O28" s="6"/>
       <c r="P28" s="10"/>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -1759,7 +1169,7 @@
       <c r="O29" s="6"/>
       <c r="P29" s="10"/>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -1777,7 +1187,7 @@
       <c r="O30" s="6"/>
       <c r="P30" s="10"/>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -1795,7 +1205,7 @@
       <c r="O31" s="6"/>
       <c r="P31" s="10"/>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -1813,7 +1223,7 @@
       <c r="O32" s="6"/>
       <c r="P32" s="10"/>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -1831,7 +1241,7 @@
       <c r="O33" s="6"/>
       <c r="P33" s="10"/>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -1849,7 +1259,7 @@
       <c r="O34" s="6"/>
       <c r="P34" s="10"/>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1867,7 +1277,7 @@
       <c r="O35" s="6"/>
       <c r="P35" s="10"/>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -1885,7 +1295,7 @@
       <c r="O36" s="6"/>
       <c r="P36" s="10"/>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1903,7 +1313,7 @@
       <c r="O37" s="6"/>
       <c r="P37" s="10"/>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" s="8"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1921,7 +1331,7 @@
       <c r="O38" s="6"/>
       <c r="P38" s="10"/>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="8"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1939,7 +1349,7 @@
       <c r="O39" s="6"/>
       <c r="P39" s="10"/>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" s="8"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1957,7 +1367,7 @@
       <c r="O40" s="6"/>
       <c r="P40" s="10"/>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" s="8"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1975,7 +1385,7 @@
       <c r="O41" s="6"/>
       <c r="P41" s="10"/>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="8"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -1993,7 +1403,7 @@
       <c r="O42" s="6"/>
       <c r="P42" s="10"/>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="8"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -2011,7 +1421,7 @@
       <c r="O43" s="6"/>
       <c r="P43" s="10"/>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" s="8"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -2029,7 +1439,7 @@
       <c r="O44" s="6"/>
       <c r="P44" s="10"/>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="8"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -2047,7 +1457,7 @@
       <c r="O45" s="6"/>
       <c r="P45" s="10"/>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" s="8"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -2065,7 +1475,7 @@
       <c r="O46" s="6"/>
       <c r="P46" s="10"/>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" s="8"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -2083,7 +1493,7 @@
       <c r="O47" s="6"/>
       <c r="P47" s="10"/>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" s="8"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -2101,7 +1511,7 @@
       <c r="O48" s="6"/>
       <c r="P48" s="10"/>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="8"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -2119,7 +1529,7 @@
       <c r="O49" s="6"/>
       <c r="P49" s="10"/>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" s="8"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -2137,7 +1547,7 @@
       <c r="O50" s="6"/>
       <c r="P50" s="10"/>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" s="8"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -2155,7 +1565,7 @@
       <c r="O51" s="6"/>
       <c r="P51" s="10"/>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" s="8"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -2173,7 +1583,7 @@
       <c r="O52" s="6"/>
       <c r="P52" s="10"/>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" s="8"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -2191,7 +1601,7 @@
       <c r="O53" s="6"/>
       <c r="P53" s="10"/>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" s="8"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -2209,7 +1619,7 @@
       <c r="O54" s="6"/>
       <c r="P54" s="10"/>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" s="8"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -2227,7 +1637,7 @@
       <c r="O55" s="6"/>
       <c r="P55" s="10"/>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" s="8"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -2245,7 +1655,7 @@
       <c r="O56" s="6"/>
       <c r="P56" s="10"/>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" s="8"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -2263,7 +1673,7 @@
       <c r="O57" s="6"/>
       <c r="P57" s="10"/>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" s="8"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -2281,7 +1691,7 @@
       <c r="O58" s="6"/>
       <c r="P58" s="10"/>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" s="8"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -2299,7 +1709,7 @@
       <c r="O59" s="6"/>
       <c r="P59" s="10"/>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" s="8"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -2317,7 +1727,7 @@
       <c r="O60" s="6"/>
       <c r="P60" s="10"/>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" s="8"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -2335,7 +1745,7 @@
       <c r="O61" s="6"/>
       <c r="P61" s="10"/>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" s="8"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -2353,7 +1763,7 @@
       <c r="O62" s="6"/>
       <c r="P62" s="10"/>
     </row>
-    <row r="63" spans="1:16">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" s="8"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -2371,7 +1781,7 @@
       <c r="O63" s="6"/>
       <c r="P63" s="10"/>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" s="8"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -2389,7 +1799,7 @@
       <c r="O64" s="6"/>
       <c r="P64" s="10"/>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" s="8"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -2407,7 +1817,7 @@
       <c r="O65" s="6"/>
       <c r="P65" s="10"/>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" s="8"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -2425,7 +1835,7 @@
       <c r="O66" s="6"/>
       <c r="P66" s="10"/>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" s="8"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -2443,7 +1853,7 @@
       <c r="O67" s="6"/>
       <c r="P67" s="10"/>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68" s="8"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -2461,7 +1871,7 @@
       <c r="O68" s="6"/>
       <c r="P68" s="10"/>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69" s="8"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -2479,7 +1889,7 @@
       <c r="O69" s="6"/>
       <c r="P69" s="10"/>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70" s="8"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -2497,7 +1907,7 @@
       <c r="O70" s="6"/>
       <c r="P70" s="10"/>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71" s="8"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -2515,7 +1925,7 @@
       <c r="O71" s="6"/>
       <c r="P71" s="10"/>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72" s="8"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -2533,7 +1943,7 @@
       <c r="O72" s="6"/>
       <c r="P72" s="10"/>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73" s="8"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -2551,7 +1961,7 @@
       <c r="O73" s="6"/>
       <c r="P73" s="10"/>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" s="8"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -2569,7 +1979,7 @@
       <c r="O74" s="6"/>
       <c r="P74" s="10"/>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75" s="8"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -2587,7 +1997,7 @@
       <c r="O75" s="6"/>
       <c r="P75" s="10"/>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76" s="8"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -2605,7 +2015,7 @@
       <c r="O76" s="6"/>
       <c r="P76" s="10"/>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77" s="8"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -2623,7 +2033,7 @@
       <c r="O77" s="6"/>
       <c r="P77" s="10"/>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78" s="8"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -2641,7 +2051,7 @@
       <c r="O78" s="6"/>
       <c r="P78" s="10"/>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79" s="8"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -2659,7 +2069,7 @@
       <c r="O79" s="6"/>
       <c r="P79" s="10"/>
     </row>
-    <row r="80" spans="1:16">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80" s="8"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -2677,7 +2087,7 @@
       <c r="O80" s="6"/>
       <c r="P80" s="10"/>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81" s="8"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -2695,7 +2105,7 @@
       <c r="O81" s="6"/>
       <c r="P81" s="10"/>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82" s="8"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -2713,7 +2123,7 @@
       <c r="O82" s="6"/>
       <c r="P82" s="10"/>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A83" s="8"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -2731,7 +2141,7 @@
       <c r="O83" s="6"/>
       <c r="P83" s="10"/>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84" s="8"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -2749,7 +2159,7 @@
       <c r="O84" s="6"/>
       <c r="P84" s="10"/>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85" s="8"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -2767,7 +2177,7 @@
       <c r="O85" s="6"/>
       <c r="P85" s="10"/>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86" s="8"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -2785,7 +2195,7 @@
       <c r="O86" s="6"/>
       <c r="P86" s="10"/>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87" s="8"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -2803,7 +2213,7 @@
       <c r="O87" s="6"/>
       <c r="P87" s="10"/>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88" s="8"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2821,7 +2231,7 @@
       <c r="O88" s="6"/>
       <c r="P88" s="10"/>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89" s="8"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2839,7 +2249,7 @@
       <c r="O89" s="6"/>
       <c r="P89" s="10"/>
     </row>
-    <row r="90" spans="1:16">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90" s="8"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2857,7 +2267,7 @@
       <c r="O90" s="6"/>
       <c r="P90" s="10"/>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91" s="8"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2875,7 +2285,7 @@
       <c r="O91" s="6"/>
       <c r="P91" s="10"/>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A92" s="8"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2893,7 +2303,7 @@
       <c r="O92" s="6"/>
       <c r="P92" s="10"/>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A93" s="8"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2911,7 +2321,7 @@
       <c r="O93" s="6"/>
       <c r="P93" s="10"/>
     </row>
-    <row r="94" spans="1:16">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A94" s="8"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2929,7 +2339,7 @@
       <c r="O94" s="6"/>
       <c r="P94" s="10"/>
     </row>
-    <row r="95" spans="1:16">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95" s="8"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2947,7 +2357,7 @@
       <c r="O95" s="6"/>
       <c r="P95" s="10"/>
     </row>
-    <row r="96" spans="1:16">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A96" s="8"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -2965,7 +2375,7 @@
       <c r="O96" s="6"/>
       <c r="P96" s="10"/>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A97" s="8"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -2983,7 +2393,7 @@
       <c r="O97" s="6"/>
       <c r="P97" s="10"/>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A98" s="8"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -3001,7 +2411,7 @@
       <c r="O98" s="6"/>
       <c r="P98" s="10"/>
     </row>
-    <row r="99" spans="1:16">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A99" s="8"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -3019,7 +2429,7 @@
       <c r="O99" s="6"/>
       <c r="P99" s="10"/>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A100" s="8"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -3037,7 +2447,7 @@
       <c r="O100" s="6"/>
       <c r="P100" s="10"/>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A101" s="8"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -3055,1129 +2465,1129 @@
       <c r="O101" s="6"/>
       <c r="P101" s="10"/>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A102" s="11"/>
       <c r="H102" s="12"/>
       <c r="K102" s="13"/>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103" s="11"/>
       <c r="H103" s="12"/>
       <c r="K103" s="13"/>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A104" s="11"/>
       <c r="H104" s="12"/>
       <c r="K104" s="13"/>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A105" s="11"/>
       <c r="H105" s="12"/>
       <c r="K105" s="13"/>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A106" s="11"/>
       <c r="H106" s="12"/>
       <c r="K106" s="13"/>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A107" s="11"/>
       <c r="H107" s="12"/>
       <c r="K107" s="13"/>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108" s="11"/>
       <c r="H108" s="12"/>
       <c r="K108" s="13"/>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A109" s="11"/>
       <c r="H109" s="12"/>
       <c r="K109" s="13"/>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A110" s="11"/>
       <c r="H110" s="12"/>
       <c r="K110" s="13"/>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A111" s="11"/>
       <c r="H111" s="12"/>
       <c r="K111" s="13"/>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A112" s="11"/>
       <c r="H112" s="12"/>
       <c r="K112" s="13"/>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" s="11"/>
       <c r="H113" s="12"/>
       <c r="K113" s="13"/>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" s="11"/>
       <c r="H114" s="12"/>
       <c r="K114" s="13"/>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" s="11"/>
       <c r="H115" s="12"/>
       <c r="K115" s="13"/>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116" s="11"/>
       <c r="H116" s="12"/>
       <c r="K116" s="13"/>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117" s="11"/>
       <c r="H117" s="12"/>
       <c r="K117" s="13"/>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118" s="11"/>
       <c r="H118" s="12"/>
       <c r="K118" s="13"/>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119" s="11"/>
       <c r="H119" s="12"/>
       <c r="K119" s="13"/>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120" s="11"/>
       <c r="H120" s="12"/>
       <c r="K120" s="13"/>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" s="11"/>
       <c r="H121" s="12"/>
       <c r="K121" s="13"/>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122" s="11"/>
       <c r="H122" s="12"/>
       <c r="K122" s="13"/>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123" s="11"/>
       <c r="H123" s="12"/>
       <c r="K123" s="13"/>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" s="11"/>
       <c r="H124" s="12"/>
       <c r="K124" s="13"/>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" s="11"/>
       <c r="H125" s="12"/>
       <c r="K125" s="13"/>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" s="11"/>
       <c r="H126" s="12"/>
       <c r="K126" s="13"/>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" s="11"/>
       <c r="H127" s="12"/>
       <c r="K127" s="13"/>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" s="11"/>
       <c r="H128" s="12"/>
       <c r="K128" s="13"/>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A129" s="11"/>
       <c r="H129" s="12"/>
       <c r="K129" s="13"/>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A130" s="11"/>
       <c r="H130" s="12"/>
       <c r="K130" s="13"/>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A131" s="11"/>
       <c r="H131" s="12"/>
       <c r="K131" s="13"/>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A132" s="11"/>
       <c r="H132" s="12"/>
       <c r="K132" s="13"/>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A133" s="11"/>
       <c r="H133" s="12"/>
       <c r="K133" s="13"/>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134" s="11"/>
       <c r="H134" s="12"/>
       <c r="K134" s="13"/>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135" s="11"/>
       <c r="H135" s="12"/>
       <c r="K135" s="13"/>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136" s="11"/>
       <c r="H136" s="12"/>
       <c r="K136" s="13"/>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A137" s="11"/>
       <c r="H137" s="12"/>
       <c r="K137" s="13"/>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A138" s="11"/>
       <c r="H138" s="12"/>
       <c r="K138" s="13"/>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A139" s="11"/>
       <c r="H139" s="12"/>
       <c r="K139" s="13"/>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A140" s="11"/>
       <c r="H140" s="12"/>
       <c r="K140" s="13"/>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A141" s="11"/>
       <c r="H141" s="12"/>
       <c r="K141" s="13"/>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A142" s="11"/>
       <c r="H142" s="12"/>
       <c r="K142" s="13"/>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A143" s="11"/>
       <c r="H143" s="12"/>
       <c r="K143" s="13"/>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A144" s="11"/>
       <c r="H144" s="12"/>
       <c r="K144" s="13"/>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A145" s="11"/>
       <c r="H145" s="12"/>
       <c r="K145" s="13"/>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A146" s="11"/>
       <c r="H146" s="12"/>
       <c r="K146" s="13"/>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A147" s="11"/>
       <c r="H147" s="12"/>
       <c r="K147" s="13"/>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A148" s="11"/>
       <c r="H148" s="12"/>
       <c r="K148" s="13"/>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A149" s="11"/>
       <c r="H149" s="12"/>
       <c r="K149" s="13"/>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A150" s="11"/>
       <c r="H150" s="12"/>
       <c r="K150" s="13"/>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A151" s="11"/>
       <c r="H151" s="12"/>
       <c r="K151" s="13"/>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A152" s="11"/>
       <c r="H152" s="12"/>
       <c r="K152" s="13"/>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" s="11"/>
       <c r="H153" s="12"/>
       <c r="K153" s="13"/>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154" s="11"/>
       <c r="H154" s="12"/>
       <c r="K154" s="13"/>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155" s="11"/>
       <c r="H155" s="12"/>
       <c r="K155" s="13"/>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156" s="11"/>
       <c r="H156" s="12"/>
       <c r="K156" s="13"/>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157" s="11"/>
       <c r="H157" s="12"/>
       <c r="K157" s="13"/>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158" s="11"/>
       <c r="H158" s="12"/>
       <c r="K158" s="13"/>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" s="11"/>
       <c r="H159" s="12"/>
       <c r="K159" s="13"/>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160" s="11"/>
       <c r="H160" s="12"/>
       <c r="K160" s="13"/>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161" s="11"/>
       <c r="H161" s="12"/>
       <c r="K161" s="13"/>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A162" s="11"/>
       <c r="H162" s="12"/>
       <c r="K162" s="13"/>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A163" s="11"/>
       <c r="H163" s="12"/>
       <c r="K163" s="13"/>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" s="11"/>
       <c r="H164" s="12"/>
       <c r="K164" s="13"/>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A165" s="11"/>
       <c r="H165" s="12"/>
       <c r="K165" s="13"/>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A166" s="11"/>
       <c r="H166" s="12"/>
       <c r="K166" s="13"/>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A167" s="11"/>
       <c r="H167" s="12"/>
       <c r="K167" s="13"/>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A168" s="11"/>
       <c r="H168" s="12"/>
       <c r="K168" s="13"/>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A169" s="11"/>
       <c r="H169" s="12"/>
       <c r="K169" s="13"/>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A170" s="11"/>
       <c r="H170" s="12"/>
       <c r="K170" s="13"/>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A171" s="11"/>
       <c r="H171" s="12"/>
       <c r="K171" s="13"/>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A172" s="11"/>
       <c r="H172" s="12"/>
       <c r="K172" s="13"/>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A173" s="11"/>
       <c r="H173" s="12"/>
       <c r="K173" s="13"/>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A174" s="11"/>
       <c r="H174" s="12"/>
       <c r="K174" s="13"/>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A175" s="11"/>
       <c r="H175" s="12"/>
       <c r="K175" s="13"/>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A176" s="11"/>
       <c r="H176" s="12"/>
       <c r="K176" s="13"/>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A177" s="11"/>
       <c r="H177" s="12"/>
       <c r="K177" s="13"/>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A178" s="11"/>
       <c r="H178" s="12"/>
       <c r="K178" s="13"/>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179" s="11"/>
       <c r="H179" s="12"/>
       <c r="K179" s="13"/>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180" s="11"/>
       <c r="H180" s="12"/>
       <c r="K180" s="13"/>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181" s="11"/>
       <c r="H181" s="12"/>
       <c r="K181" s="13"/>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A182" s="11"/>
       <c r="H182" s="12"/>
       <c r="K182" s="13"/>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A183" s="11"/>
       <c r="H183" s="12"/>
       <c r="K183" s="13"/>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A184" s="11"/>
       <c r="H184" s="12"/>
       <c r="K184" s="13"/>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A185" s="11"/>
       <c r="H185" s="12"/>
       <c r="K185" s="13"/>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A186" s="11"/>
       <c r="H186" s="12"/>
       <c r="K186" s="13"/>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A187" s="11"/>
       <c r="H187" s="12"/>
       <c r="K187" s="13"/>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A188" s="11"/>
       <c r="H188" s="12"/>
       <c r="K188" s="13"/>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A189" s="11"/>
       <c r="H189" s="12"/>
       <c r="K189" s="13"/>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190" s="11"/>
       <c r="H190" s="12"/>
       <c r="K190" s="13"/>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A191" s="11"/>
       <c r="H191" s="12"/>
       <c r="K191" s="13"/>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A192" s="11"/>
       <c r="H192" s="12"/>
       <c r="K192" s="13"/>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A193" s="11"/>
       <c r="H193" s="12"/>
       <c r="K193" s="13"/>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A194" s="11"/>
       <c r="H194" s="12"/>
       <c r="K194" s="13"/>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A195" s="11"/>
       <c r="H195" s="12"/>
       <c r="K195" s="13"/>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A196" s="11"/>
       <c r="H196" s="12"/>
       <c r="K196" s="13"/>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A197" s="11"/>
       <c r="H197" s="12"/>
       <c r="K197" s="13"/>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A198" s="11"/>
       <c r="H198" s="12"/>
       <c r="K198" s="13"/>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A199" s="11"/>
       <c r="H199" s="12"/>
       <c r="K199" s="13"/>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A200" s="11"/>
       <c r="H200" s="12"/>
       <c r="K200" s="13"/>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A201" s="11"/>
       <c r="H201" s="12"/>
       <c r="K201" s="13"/>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A202" s="11"/>
       <c r="H202" s="12"/>
       <c r="K202" s="13"/>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A203" s="11"/>
       <c r="H203" s="12"/>
       <c r="K203" s="13"/>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A204" s="11"/>
       <c r="H204" s="12"/>
       <c r="K204" s="13"/>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A205" s="11"/>
       <c r="H205" s="12"/>
       <c r="K205" s="13"/>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A206" s="11"/>
       <c r="H206" s="12"/>
       <c r="K206" s="13"/>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A207" s="11"/>
       <c r="H207" s="12"/>
       <c r="K207" s="13"/>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A208" s="11"/>
       <c r="H208" s="12"/>
       <c r="K208" s="13"/>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A209" s="11"/>
       <c r="H209" s="12"/>
       <c r="K209" s="13"/>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A210" s="11"/>
       <c r="H210" s="12"/>
       <c r="K210" s="13"/>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A211" s="11"/>
       <c r="H211" s="12"/>
       <c r="K211" s="13"/>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A212" s="11"/>
       <c r="H212" s="12"/>
       <c r="K212" s="13"/>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A213" s="11"/>
       <c r="H213" s="12"/>
       <c r="K213" s="13"/>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A214" s="11"/>
       <c r="H214" s="12"/>
       <c r="K214" s="13"/>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A215" s="11"/>
       <c r="H215" s="12"/>
       <c r="K215" s="13"/>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A216" s="11"/>
       <c r="H216" s="12"/>
       <c r="K216" s="13"/>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A217" s="11"/>
       <c r="H217" s="12"/>
       <c r="K217" s="13"/>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A218" s="11"/>
       <c r="H218" s="12"/>
       <c r="K218" s="13"/>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A219" s="11"/>
       <c r="H219" s="12"/>
       <c r="K219" s="13"/>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A220" s="11"/>
       <c r="H220" s="12"/>
       <c r="K220" s="13"/>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A221" s="11"/>
       <c r="H221" s="12"/>
       <c r="K221" s="13"/>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A222" s="11"/>
       <c r="H222" s="12"/>
       <c r="K222" s="13"/>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A223" s="11"/>
       <c r="H223" s="12"/>
       <c r="K223" s="13"/>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A224" s="11"/>
       <c r="H224" s="12"/>
       <c r="K224" s="13"/>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A225" s="11"/>
       <c r="H225" s="12"/>
       <c r="K225" s="13"/>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A226" s="11"/>
       <c r="H226" s="12"/>
       <c r="K226" s="13"/>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A227" s="11"/>
       <c r="H227" s="12"/>
       <c r="K227" s="13"/>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A228" s="11"/>
       <c r="H228" s="12"/>
       <c r="K228" s="13"/>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A229" s="11"/>
       <c r="H229" s="12"/>
       <c r="K229" s="13"/>
     </row>
-    <row r="230" spans="1:11">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A230" s="11"/>
       <c r="H230" s="12"/>
       <c r="K230" s="13"/>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A231" s="11"/>
       <c r="H231" s="12"/>
       <c r="K231" s="13"/>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A232" s="11"/>
       <c r="H232" s="12"/>
       <c r="K232" s="13"/>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A233" s="11"/>
       <c r="H233" s="12"/>
       <c r="K233" s="13"/>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A234" s="11"/>
       <c r="H234" s="12"/>
       <c r="K234" s="13"/>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A235" s="11"/>
       <c r="H235" s="12"/>
       <c r="K235" s="13"/>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A236" s="11"/>
       <c r="H236" s="12"/>
       <c r="K236" s="13"/>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A237" s="11"/>
       <c r="H237" s="12"/>
       <c r="K237" s="13"/>
     </row>
-    <row r="238" spans="1:11">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A238" s="11"/>
       <c r="H238" s="12"/>
       <c r="K238" s="13"/>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A239" s="11"/>
       <c r="H239" s="12"/>
       <c r="K239" s="13"/>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A240" s="11"/>
       <c r="H240" s="12"/>
       <c r="K240" s="13"/>
     </row>
-    <row r="241" spans="1:11">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A241" s="11"/>
       <c r="H241" s="12"/>
       <c r="K241" s="13"/>
     </row>
-    <row r="242" spans="1:11">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A242" s="11"/>
       <c r="H242" s="12"/>
       <c r="K242" s="13"/>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A243" s="11"/>
       <c r="H243" s="12"/>
       <c r="K243" s="13"/>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A244" s="11"/>
       <c r="H244" s="12"/>
       <c r="K244" s="13"/>
     </row>
-    <row r="245" spans="1:11">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A245" s="11"/>
       <c r="H245" s="12"/>
       <c r="K245" s="13"/>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A246" s="11"/>
       <c r="H246" s="12"/>
       <c r="K246" s="13"/>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A247" s="11"/>
       <c r="H247" s="12"/>
       <c r="K247" s="13"/>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A248" s="11"/>
       <c r="H248" s="12"/>
       <c r="K248" s="13"/>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A249" s="11"/>
       <c r="H249" s="12"/>
       <c r="K249" s="13"/>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A250" s="11"/>
       <c r="H250" s="12"/>
       <c r="K250" s="13"/>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A251" s="11"/>
       <c r="H251" s="12"/>
       <c r="K251" s="13"/>
     </row>
-    <row r="252" spans="1:11">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A252" s="11"/>
       <c r="H252" s="12"/>
       <c r="K252" s="13"/>
     </row>
-    <row r="253" spans="1:11">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A253" s="11"/>
       <c r="H253" s="12"/>
       <c r="K253" s="13"/>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A254" s="11"/>
       <c r="H254" s="12"/>
       <c r="K254" s="13"/>
     </row>
-    <row r="255" spans="1:11">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A255" s="11"/>
       <c r="H255" s="12"/>
       <c r="K255" s="13"/>
     </row>
-    <row r="256" spans="1:11">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A256" s="11"/>
       <c r="H256" s="12"/>
       <c r="K256" s="13"/>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A257" s="11"/>
       <c r="H257" s="12"/>
       <c r="K257" s="13"/>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A258" s="11"/>
       <c r="H258" s="12"/>
       <c r="K258" s="13"/>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A259" s="11"/>
       <c r="H259" s="12"/>
       <c r="K259" s="13"/>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A260" s="11"/>
       <c r="H260" s="12"/>
       <c r="K260" s="13"/>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A261" s="11"/>
       <c r="H261" s="12"/>
       <c r="K261" s="13"/>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A262" s="11"/>
       <c r="H262" s="12"/>
       <c r="K262" s="13"/>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A263" s="11"/>
       <c r="H263" s="12"/>
       <c r="K263" s="13"/>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A264" s="11"/>
       <c r="H264" s="12"/>
       <c r="K264" s="13"/>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A265" s="11"/>
       <c r="H265" s="12"/>
       <c r="K265" s="13"/>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A266" s="11"/>
       <c r="H266" s="12"/>
       <c r="K266" s="13"/>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A267" s="11"/>
       <c r="H267" s="12"/>
       <c r="K267" s="13"/>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A268" s="11"/>
       <c r="H268" s="12"/>
       <c r="K268" s="13"/>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A269" s="11"/>
       <c r="H269" s="12"/>
       <c r="K269" s="13"/>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A270" s="11"/>
       <c r="H270" s="12"/>
       <c r="K270" s="13"/>
     </row>
-    <row r="271" spans="1:11">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A271" s="11"/>
       <c r="H271" s="12"/>
       <c r="K271" s="13"/>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A272" s="11"/>
       <c r="H272" s="12"/>
       <c r="K272" s="13"/>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A273" s="11"/>
       <c r="H273" s="12"/>
       <c r="K273" s="13"/>
     </row>
-    <row r="274" spans="1:11">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A274" s="11"/>
       <c r="H274" s="12"/>
       <c r="K274" s="13"/>
     </row>
-    <row r="275" spans="1:11">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A275" s="11"/>
       <c r="H275" s="12"/>
       <c r="K275" s="13"/>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A276" s="11"/>
       <c r="H276" s="12"/>
       <c r="K276" s="13"/>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A277" s="11"/>
       <c r="H277" s="12"/>
       <c r="K277" s="13"/>
     </row>
-    <row r="278" spans="1:11">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A278" s="11"/>
       <c r="H278" s="12"/>
       <c r="K278" s="13"/>
     </row>
-    <row r="279" spans="1:11">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A279" s="11"/>
       <c r="H279" s="12"/>
       <c r="K279" s="13"/>
     </row>
-    <row r="280" spans="1:11">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A280" s="11"/>
       <c r="H280" s="12"/>
       <c r="K280" s="13"/>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A281" s="11"/>
       <c r="H281" s="12"/>
       <c r="K281" s="13"/>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A282" s="11"/>
       <c r="H282" s="12"/>
       <c r="K282" s="13"/>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A283" s="11"/>
       <c r="H283" s="12"/>
       <c r="K283" s="13"/>
     </row>
-    <row r="284" spans="1:11">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A284" s="11"/>
       <c r="H284" s="12"/>
       <c r="K284" s="13"/>
     </row>
-    <row r="285" spans="1:11">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A285" s="11"/>
       <c r="H285" s="12"/>
       <c r="K285" s="13"/>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A286" s="11"/>
       <c r="H286" s="12"/>
       <c r="K286" s="13"/>
     </row>
-    <row r="287" spans="1:11">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A287" s="11"/>
       <c r="H287" s="12"/>
       <c r="K287" s="13"/>
     </row>
-    <row r="288" spans="1:11">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A288" s="11"/>
       <c r="H288" s="12"/>
       <c r="K288" s="13"/>
     </row>
-    <row r="289" spans="1:11">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A289" s="11"/>
       <c r="H289" s="12"/>
       <c r="K289" s="13"/>
     </row>
-    <row r="290" spans="1:11">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A290" s="11"/>
       <c r="H290" s="12"/>
       <c r="K290" s="13"/>
     </row>
-    <row r="291" spans="1:11">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A291" s="11"/>
       <c r="H291" s="12"/>
       <c r="K291" s="13"/>
     </row>
-    <row r="292" spans="1:11">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A292" s="11"/>
       <c r="H292" s="12"/>
       <c r="K292" s="13"/>
     </row>
-    <row r="293" spans="1:11">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A293" s="11"/>
       <c r="H293" s="12"/>
       <c r="K293" s="13"/>
     </row>
-    <row r="294" spans="1:11">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A294" s="11"/>
       <c r="H294" s="12"/>
       <c r="K294" s="13"/>
     </row>
-    <row r="295" spans="1:11">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A295" s="11"/>
       <c r="H295" s="12"/>
       <c r="K295" s="13"/>
     </row>
-    <row r="296" spans="1:1">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A296" s="11"/>
     </row>
-    <row r="297" spans="1:1">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A297" s="11"/>
     </row>
-    <row r="298" spans="1:1">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A298" s="11"/>
     </row>
-    <row r="299" spans="1:1">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A299" s="11"/>
     </row>
-    <row r="300" spans="1:1">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A300" s="11"/>
     </row>
-    <row r="301" spans="1:1">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A301" s="11"/>
     </row>
-    <row r="302" spans="1:1">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A302" s="11"/>
     </row>
-    <row r="303" spans="1:1">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A303" s="11"/>
     </row>
-    <row r="304" spans="1:1">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A304" s="11"/>
     </row>
-    <row r="305" spans="1:1">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A305" s="11"/>
     </row>
-    <row r="306" spans="1:1">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A306" s="11"/>
     </row>
-    <row r="307" spans="1:1">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A307" s="11"/>
     </row>
-    <row r="308" spans="1:1">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A308" s="11"/>
     </row>
-    <row r="309" spans="1:1">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A309" s="11"/>
     </row>
-    <row r="310" spans="1:1">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A310" s="11"/>
     </row>
-    <row r="311" spans="1:1">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A311" s="11"/>
     </row>
-    <row r="312" spans="1:1">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A312" s="11"/>
     </row>
-    <row r="313" spans="1:1">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A313" s="11"/>
     </row>
-    <row r="314" spans="1:1">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A314" s="11"/>
     </row>
-    <row r="315" spans="1:1">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A315" s="11"/>
     </row>
-    <row r="316" spans="1:1">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A316" s="11"/>
     </row>
-    <row r="317" spans="1:1">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A317" s="11"/>
     </row>
-    <row r="318" spans="1:1">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A318" s="11"/>
     </row>
-    <row r="319" spans="1:1">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A319" s="11"/>
     </row>
-    <row r="320" spans="1:1">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A320" s="11"/>
     </row>
-    <row r="321" spans="1:1">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A321" s="11"/>
     </row>
-    <row r="322" spans="1:1">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A322" s="11"/>
     </row>
-    <row r="323" spans="1:1">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A323" s="11"/>
     </row>
-    <row r="324" spans="1:1">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A324" s="11"/>
     </row>
-    <row r="325" spans="1:1">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A325" s="11"/>
     </row>
-    <row r="326" spans="1:1">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A326" s="11"/>
     </row>
-    <row r="327" spans="1:1">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A327" s="11"/>
     </row>
-    <row r="328" spans="1:1">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A328" s="11"/>
     </row>
-    <row r="329" spans="1:1">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A329" s="11"/>
     </row>
-    <row r="330" spans="1:1">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A330" s="11"/>
     </row>
-    <row r="331" spans="1:1">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A331" s="11"/>
     </row>
-    <row r="332" spans="1:1">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A332" s="11"/>
     </row>
-    <row r="333" spans="1:1">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A333" s="11"/>
     </row>
-    <row r="334" spans="1:1">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A334" s="11"/>
     </row>
-    <row r="335" spans="1:1">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A335" s="11"/>
     </row>
-    <row r="336" spans="1:1">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A336" s="11"/>
     </row>
-    <row r="337" spans="1:1">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A337" s="11"/>
     </row>
-    <row r="338" spans="1:1">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A338" s="11"/>
     </row>
-    <row r="339" spans="1:1">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A339" s="11"/>
     </row>
-    <row r="340" spans="1:1">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A340" s="11"/>
     </row>
-    <row r="341" spans="1:1">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A341" s="11"/>
     </row>
-    <row r="342" spans="1:1">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A342" s="11"/>
     </row>
-    <row r="343" spans="1:1">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A343" s="11"/>
     </row>
-    <row r="344" spans="1:1">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A344" s="11"/>
     </row>
-    <row r="345" spans="1:1">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A345" s="11"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>